--- a/samples/ss_krian3456_ingest.xlsx
+++ b/samples/ss_krian3456_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,65 +535,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -632,24 +637,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -685,37 +691,42 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>KRIAN7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>KRIAN</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>3 IBT x 500 MVA (unit 3,4,5) 500/150/66 kV</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -751,41 +762,46 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>KRIAN7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>KRIAN</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>1 IBT x 500 MVA; sementara sampai SUTET 500 kV siap</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -818,30 +834,31 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>bus A1/A2 - B1/B2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -874,34 +891,35 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>3x60 MVA</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -934,34 +952,35 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>50/50/60 MVA</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -994,30 +1013,31 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>4x60 MVA + 50 MVAR</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1050,34 +1070,35 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>60 MVA (bay 3,4,9,10)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1110,34 +1131,35 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>T/L bay Surabaya Barat single phi</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1173,41 +1195,46 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>DRYJO5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>DRYJO4</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>kapasitas IBT tidak seimbang</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1240,34 +1267,35 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>single busbar; 30 MVA (bay 8)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1300,34 +1328,35 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>single busbar; 30 MVA</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1360,30 +1389,31 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>60/40 MVA</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1416,30 +1446,31 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>20/12 MVA</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1472,30 +1503,31 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>30/30/10 MVA</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1528,30 +1560,31 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>30 MVA</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_krian3456_ingest.xlsx
+++ b/samples/ss_krian3456_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3,4,5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_krian3456_ingest.xlsx
+++ b/samples/ss_krian3456_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 3,4,5 Krian 500/150/66 kV</t>
+          <t>IBT 3 Krian 500/150/66 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,4,5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>3 IBT x 500 MVA (unit 3,4,5) 500/150/66 kV</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBT 6 Krian 500/150/66 kV (sementara)</t>
+          <t>IBT 4 Krian 500/150/66 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IBT 6 KRIAN7</t>
+          <t>IBT 4 KRIAN7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -757,7 +753,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -774,11 +770,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1 IBT x 500 MVA; sementara sampai SUTET 500 kV siap</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -788,14 +780,10 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -809,37 +797,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Krian (bus 150 kV)</t>
+          <t>IBT 5 Krian 500/150/66 kV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>IBT 5 KRIAN7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>KRIAN7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>KRIAN</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>bus A1/A2 - B1/B2</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -866,17 +864,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Surabaya Barat</t>
+          <t>IBT 6 Krian 500/150/66 kV (sementara)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SBRAT5</t>
+          <t>IBT 6 KRIAN7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -884,17 +882,31 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>KRIAN7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>KRIAN</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3x60 MVA</t>
+          <t>1 IBT x 500 MVA; sementara sampai SUTET 500 kV siap</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -911,7 +923,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -927,12 +939,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Balongbendo</t>
+          <t>Krian (bus 150 kV)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BBDAN</t>
+          <t>KRIAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -941,7 +953,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -955,7 +967,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50/50/60 MVA</t>
+          <t>bus A1/A2 - B1/B2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -967,14 +979,10 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -988,12 +996,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bulubendo</t>
+          <t>Surabaya Barat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLBND</t>
+          <t>SBRAT5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1016,7 +1024,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4x60 MVA + 50 MVAR</t>
+          <t>3x60 MVA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1028,10 +1036,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1045,12 +1057,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Driyorejo (bus 150 kV)</t>
+          <t>Balongbendo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DRYJO5</t>
+          <t>BBDAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1073,7 +1085,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>60 MVA (bay 3,4,9,10)</t>
+          <t>50/50/60 MVA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1090,7 +1102,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1106,12 +1118,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kasih Jatim</t>
+          <t>Bulubendo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KSJTM</t>
+          <t>BLBND</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1120,7 +1132,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1134,7 +1146,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>T/L bay Surabaya Barat single phi</t>
+          <t>4x60 MVA + 50 MVAR</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1146,14 +1158,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1167,49 +1175,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Driyorejo</t>
+          <t>Driyorejo (bus 150 kV)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IBT 1 DRYJO5</t>
+          <t>DRYJO5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>DRYJO5</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>DRYJO4</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>kapasitas IBT tidak seimbang</t>
+          <t>60 MVA (bay 3,4,9,10)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1226,7 +1220,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1242,12 +1236,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Driyorejo (bus 70 kV)</t>
+          <t>Kasih Jatim</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DRYJO4</t>
+          <t>KSJTM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1260,7 +1254,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1270,7 +1264,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>single busbar; 30 MVA (bay 8)</t>
+          <t>T/L bay Surabaya Barat single phi</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1287,7 +1281,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1303,35 +1297,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Miwon</t>
+          <t>IBT 150/70 kV Driyorejo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MIWON</t>
+          <t>IBT 1 DRYJO5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DRYJO5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DRYJO4</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>single busbar; 30 MVA</t>
+          <t>kapasitas IBT tidak seimbang</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1348,7 +1356,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1364,12 +1372,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cukir / Cikamia</t>
+          <t>Driyorejo (bus 70 kV)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CKMIA</t>
+          <t>DRYJO4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1378,7 +1386,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1392,7 +1400,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>60/40 MVA</t>
+          <t>single busbar; 30 MVA (bay 8)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1404,10 +1412,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1421,12 +1433,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajimoto</t>
+          <t>Miwon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AJMTO</t>
+          <t>MIWON</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1449,7 +1461,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>20/12 MVA</t>
+          <t>single busbar; 30 MVA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1461,10 +1473,14 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1478,12 +1494,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tarik</t>
+          <t>Cukir / Cikamia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TARIK</t>
+          <t>CKMIA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1506,7 +1522,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30/30/10 MVA</t>
+          <t>60/40 MVA</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1535,12 +1551,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bangun</t>
+          <t>Ajimoto</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BNGUN</t>
+          <t>AJMTO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1549,7 +1565,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1563,7 +1579,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30 MVA</t>
+          <t>20/12 MVA</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1585,6 +1601,120 @@
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tarik</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TARIK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>30/30/10 MVA</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bangun</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BNGUN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>30 MVA</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2508,12 +2638,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan tidak seimbang karena konfigurasi single phi di GI Kasih Jatim T/L bay Surabaya Barat dan T/L Bay Cerme sudah berbeban diatas 60% apabila trip 1 sirkit SUTT 150 kV Kasih jatim-Cerme atau Kasih Jatim- Surabaya Barat maka terjadiOverload</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan tidak seimbang karena konfigurasi single phi di GI Kasih Jatim T/L bay Surabaya Barat dan T/L Bay Cerme sudah berbeban diatas 60% apabila trip 1 sirkit SUTT 150 kV Kasih jatim-Cerme atau Kasih Jatim- Surabaya Barat maka terjadiOverload</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2648,12 +2778,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] GI 70 kV Driyorejo hanya single Busbar</t>
+          <t>[BELUM_DITETAPKAN] GI 70 kV Driyorejo hanya single Busbar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2683,12 +2813,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan tidak seimbang kerena konfigurasi single phi di GI 70 kV Miwon T/L bay Driyorejo dan T/L Bay Tarik, beban lebih cenderung lebih besar ke arah T/L bay Miwon dan sudah berbeban diatas 70%</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan tidak seimbang kerena konfigurasi single phi di GI 70 kV Miwon T/L bay Driyorejo dan T/L Bay Tarik, beban lebih cenderung lebih besar ke arah T/L bay Miwon dan sudah berbeban diatas 70%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2718,12 +2848,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] GI 70 kV Miwon hanya single Busbar</t>
+          <t>[BELUM_DITETAPKAN] GI 70 kV Miwon hanya single Busbar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
